--- a/OpticalRx/Fabrication/BOM_OpticalInOut.xlsx
+++ b/OpticalRx/Fabrication/BOM_OpticalInOut.xlsx
@@ -354,7 +354,7 @@
     <t xml:space="preserve">    HX PZ2.0-2x5P TP</t>
   </si>
   <si>
-    <t xml:space="preserve">J2,J3,J4,J5</t>
+    <t xml:space="preserve">J2,J3,J4,J5,J6</t>
   </si>
   <si>
     <t xml:space="preserve">HC-1.25-4PWT</t>
@@ -443,7 +443,7 @@
     <t xml:space="preserve">    MLZ1005M1R0WT000</t>
   </si>
   <si>
-    <t xml:space="preserve">Q1,Q3,Q5,Q7</t>
+    <t xml:space="preserve">Q1,Q3,Q5,Q7,Q9,Q10,Q11,Q12</t>
   </si>
   <si>
     <t xml:space="preserve">BFR93AWH6327</t>
@@ -556,6 +556,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">国巨</t>
     </r>
@@ -610,7 +611,7 @@
     <t xml:space="preserve">    RC0402FR-070RL</t>
   </si>
   <si>
-    <t xml:space="preserve">R9,R11,R14,R17</t>
+    <t xml:space="preserve">R9,R11,R14,R17,R106,R107,R108,R109</t>
   </si>
   <si>
     <t xml:space="preserve">1K</t>
@@ -634,7 +635,7 @@
     <t xml:space="preserve">RC0402FR-07220RL</t>
   </si>
   <si>
-    <t xml:space="preserve">R22,R24,R26,R28</t>
+    <t xml:space="preserve">R22,R24,R26,R28,R102,R103,R104,R105</t>
   </si>
   <si>
     <t xml:space="preserve">3K</t>
@@ -1030,7 +1031,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1072,19 +1073,7 @@
       <color theme="1"/>
       <name val="DejaVu Serif"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="DejaVu Serif"/>
-      <family val="1"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1129,7 +1118,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1154,20 +1143,12 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1370,7 +1351,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="19.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="23.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="26.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="10.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.03"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="1" width="8.59"/>
   </cols>
   <sheetData>
@@ -1400,7 +1381,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
@@ -1426,7 +1407,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
@@ -1452,7 +1433,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
@@ -1650,10 +1631,10 @@
       <c r="E11" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="6" t="s">
         <v>54</v>
       </c>
       <c r="H11" s="1" t="s">
@@ -1743,7 +1724,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>72</v>
@@ -1780,7 +1761,7 @@
       <c r="E16" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="4" t="s">
         <v>80</v>
       </c>
       <c r="G16" s="1" t="s">
@@ -1806,7 +1787,7 @@
       <c r="E17" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="4" t="s">
         <v>86</v>
       </c>
       <c r="G17" s="1" t="s">
@@ -1832,7 +1813,7 @@
       <c r="E18" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="4" t="s">
         <v>90</v>
       </c>
       <c r="G18" s="1" t="s">
@@ -1842,12 +1823,12 @@
         <v>91</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="17.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>92</v>
@@ -1858,7 +1839,7 @@
       <c r="E19" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="4" t="s">
         <v>95</v>
       </c>
       <c r="G19" s="1" t="s">
@@ -1868,7 +1849,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="17.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>19</v>
       </c>
@@ -1884,7 +1865,7 @@
       <c r="E20" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="4" t="s">
         <v>99</v>
       </c>
       <c r="G20" s="1" t="s">
@@ -1894,7 +1875,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>20</v>
       </c>
@@ -1920,7 +1901,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>22</v>
       </c>
@@ -1946,7 +1927,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>23</v>
       </c>
@@ -1972,14 +1953,14 @@
         <v>114</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <v>24</v>
       </c>
       <c r="B24" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="7" t="s">
         <v>115</v>
       </c>
       <c r="D24" s="1" t="s">
@@ -1998,12 +1979,12 @@
         <v>118</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>25</v>
       </c>
       <c r="B25" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>119</v>
@@ -2024,7 +2005,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <v>26</v>
       </c>
@@ -2050,12 +2031,12 @@
         <v>126</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>27</v>
       </c>
       <c r="B27" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>127</v>
@@ -2076,7 +2057,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
         <v>28</v>
       </c>
@@ -2102,7 +2083,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
         <v>30</v>
       </c>
@@ -2128,7 +2109,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="n">
         <v>32</v>
       </c>
@@ -2154,7 +2135,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="n">
         <v>33</v>
       </c>
@@ -2196,7 +2177,7 @@
       <c r="E32" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" s="4" t="s">
         <v>150</v>
       </c>
       <c r="G32" s="1" t="s">
@@ -2222,7 +2203,7 @@
       <c r="E33" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="F33" s="6" t="s">
+      <c r="F33" s="4" t="s">
         <v>155</v>
       </c>
       <c r="G33" s="1" t="s">
@@ -2254,7 +2235,7 @@
       <c r="G34" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="H34" s="9" t="s">
+      <c r="H34" s="5" t="s">
         <v>158</v>
       </c>
     </row>
@@ -2378,7 +2359,7 @@
       <c r="E39" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F39" s="4" t="s">
         <v>186</v>
       </c>
       <c r="G39" s="1" t="s">
